--- a/Data/matchDay.xlsx
+++ b/Data/matchDay.xlsx
@@ -451,7 +451,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1">
-        <v>45920</v>
+        <v>45927</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -475,7 +475,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1">
-        <v>45890</v>
+        <v>45896</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1">
-        <v>45919</v>
+        <v>45927</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>

--- a/Data/matchDay.xlsx
+++ b/Data/matchDay.xlsx
@@ -451,7 +451,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1">
-        <v>45927</v>
+        <v>46088</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -459,7 +459,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1">
-        <v>45890</v>
+        <v>46086</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -467,7 +467,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1">
-        <v>45920</v>
+        <v>46089</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1">
-        <v>45906</v>
+        <v>46088</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1">
-        <v>45927</v>
+        <v>46087</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
@@ -507,7 +507,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1">
-        <v>45913</v>
+        <v>46087</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>10</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1">
-        <v>45919</v>
+        <v>46088</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>11</v>
@@ -555,7 +555,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1">
-        <v>45893</v>
+        <v>46089</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -563,7 +563,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1">
-        <v>45892</v>
+        <v>46086</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>17</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1">
-        <v>45893</v>
+        <v>46088</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>19</v>

--- a/Data/matchDay.xlsx
+++ b/Data/matchDay.xlsx
@@ -443,7 +443,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1">
-        <v>45912</v>
+        <v>46095</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -451,7 +451,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1">
-        <v>46088</v>
+        <v>46095</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -459,7 +459,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1">
-        <v>46086</v>
+        <v>46093</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -467,7 +467,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1">
-        <v>46089</v>
+        <v>46095</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -475,7 +475,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1">
-        <v>45896</v>
+        <v>46094</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -483,7 +483,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1">
-        <v>45906</v>
+        <v>46095</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1">
-        <v>46088</v>
+        <v>46095</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1">
-        <v>46087</v>
+        <v>46095</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
@@ -507,7 +507,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1">
-        <v>46087</v>
+        <v>46096</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>10</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1">
-        <v>46088</v>
+        <v>46094</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>11</v>
@@ -523,7 +523,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1">
-        <v>45891</v>
+        <v>46096</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -531,7 +531,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1">
-        <v>45892</v>
+        <v>46096</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1">
-        <v>45891</v>
+        <v>46096</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>14</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1">
-        <v>45892</v>
+        <v>46093</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -555,7 +555,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1">
-        <v>46089</v>
+        <v>46096</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -563,7 +563,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1">
-        <v>46086</v>
+        <v>46095</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>17</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1">
-        <v>45892</v>
+        <v>46096</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>18</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1">
-        <v>46088</v>
+        <v>46095</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>19</v>

--- a/Data/matchDay.xlsx
+++ b/Data/matchDay.xlsx
@@ -443,7 +443,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1">
-        <v>46095</v>
+        <v>46101</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -475,7 +475,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1">
-        <v>46094</v>
+        <v>46103</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -483,7 +483,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1">
-        <v>46095</v>
+        <v>46102</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1">
-        <v>46095</v>
+        <v>46102</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
@@ -507,7 +507,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1">
-        <v>46096</v>
+        <v>46102</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>10</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1">
-        <v>46094</v>
+        <v>46100</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>11</v>
@@ -523,7 +523,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1">
-        <v>46096</v>
+        <v>46102</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -531,7 +531,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1">
-        <v>46096</v>
+        <v>46103</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1">
-        <v>46096</v>
+        <v>46103</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>14</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1">
-        <v>46093</v>
+        <v>46102</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -555,7 +555,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1">
-        <v>46096</v>
+        <v>46102</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -563,7 +563,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1">
-        <v>46095</v>
+        <v>46100</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>17</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1">
-        <v>46096</v>
+        <v>46103</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>18</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1">
-        <v>46095</v>
+        <v>46101</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>19</v>

--- a/Data/matchDay.xlsx
+++ b/Data/matchDay.xlsx
@@ -443,7 +443,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1">
-        <v>46101</v>
+        <v>46107</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -451,7 +451,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1">
-        <v>46095</v>
+        <v>46109</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -459,7 +459,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1">
-        <v>46093</v>
+        <v>46110</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -467,7 +467,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1">
-        <v>46095</v>
+        <v>46108</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -475,7 +475,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1">
-        <v>46103</v>
+        <v>46109</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -483,7 +483,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1">
-        <v>46102</v>
+        <v>46109</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1">
-        <v>46102</v>
+        <v>46108</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1">
-        <v>46095</v>
+        <v>46107</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
@@ -523,7 +523,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1">
-        <v>46102</v>
+        <v>46110</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -531,7 +531,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1">
-        <v>46103</v>
+        <v>46109</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1">
-        <v>46103</v>
+        <v>46110</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>14</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1">
-        <v>46102</v>
+        <v>46109</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -555,7 +555,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1">
-        <v>46102</v>
+        <v>46109</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1">
-        <v>46103</v>
+        <v>46110</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>18</v>

--- a/Data/matchDay.xlsx
+++ b/Data/matchDay.xlsx
@@ -443,7 +443,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1">
-        <v>46107</v>
+        <v>46115</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -451,7 +451,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1">
-        <v>46109</v>
+        <v>46114</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -459,7 +459,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1">
-        <v>46110</v>
+        <v>46115</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -467,7 +467,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1">
-        <v>46108</v>
+        <v>46114</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -475,7 +475,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1">
-        <v>46109</v>
+        <v>46117</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -483,7 +483,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1">
-        <v>46109</v>
+        <v>46115</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1">
-        <v>46107</v>
+        <v>46118</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
@@ -507,7 +507,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1">
-        <v>46102</v>
+        <v>46117</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>10</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1">
-        <v>46100</v>
+        <v>46118</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>11</v>
@@ -523,7 +523,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1">
-        <v>46110</v>
+        <v>46117</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -531,7 +531,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1">
-        <v>46109</v>
+        <v>46115</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1">
-        <v>46110</v>
+        <v>46116</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>14</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1">
-        <v>46109</v>
+        <v>46116</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -563,7 +563,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1">
-        <v>46100</v>
+        <v>46116</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>17</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1">
-        <v>46110</v>
+        <v>46116</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>18</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1">
-        <v>46101</v>
+        <v>46117</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>19</v>

--- a/Data/matchDay.xlsx
+++ b/Data/matchDay.xlsx
@@ -443,7 +443,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1">
-        <v>46115</v>
+        <v>46121</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -451,7 +451,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1">
-        <v>46114</v>
+        <v>46123</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -459,7 +459,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1">
-        <v>46115</v>
+        <v>46121</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -467,7 +467,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1">
-        <v>46114</v>
+        <v>46122</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -475,7 +475,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1">
-        <v>46117</v>
+        <v>46123</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -483,7 +483,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1">
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1">
-        <v>46108</v>
+        <v>46124</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1">
-        <v>46118</v>
+        <v>46124</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
@@ -507,7 +507,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1">
-        <v>46117</v>
+        <v>46123</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>10</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1">
-        <v>46118</v>
+        <v>46123</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>11</v>
@@ -523,7 +523,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1">
-        <v>46117</v>
+        <v>46123</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -531,7 +531,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1">
-        <v>46115</v>
+        <v>46123</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1">
-        <v>46116</v>
+        <v>46124</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>14</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1">
-        <v>46116</v>
+        <v>46124</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -555,7 +555,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1">
-        <v>46109</v>
+        <v>46124</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -563,7 +563,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1">
-        <v>46116</v>
+        <v>46123</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>17</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1">
-        <v>46116</v>
+        <v>46124</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>18</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1">
-        <v>46117</v>
+        <v>46123</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>19</v>

--- a/Data/matchDay.xlsx
+++ b/Data/matchDay.xlsx
@@ -443,7 +443,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1">
-        <v>46121</v>
+        <v>46130</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -451,7 +451,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1">
-        <v>46123</v>
+        <v>46131</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -459,7 +459,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -467,7 +467,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1">
-        <v>46122</v>
+        <v>46128</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -475,7 +475,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1">
-        <v>46123</v>
+        <v>46130</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -483,7 +483,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1">
-        <v>46122</v>
+        <v>46131</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1">
-        <v>46124</v>
+        <v>46129</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1">
-        <v>46124</v>
+        <v>46129</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
@@ -507,7 +507,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1">
-        <v>46123</v>
+        <v>46130</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>10</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1">
-        <v>46123</v>
+        <v>46130</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>11</v>
@@ -523,7 +523,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1">
-        <v>46123</v>
+        <v>46131</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -531,7 +531,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1">
-        <v>46123</v>
+        <v>46131</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1">
-        <v>46124</v>
+        <v>46130</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>14</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1">
-        <v>46124</v>
+        <v>46131</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -555,7 +555,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1">
-        <v>46124</v>
+        <v>46130</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -563,7 +563,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1">
-        <v>46123</v>
+        <v>46129</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>17</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1">
-        <v>46124</v>
+        <v>46131</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>18</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1">
-        <v>46123</v>
+        <v>46129</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>19</v>

--- a/Data/matchDay.xlsx
+++ b/Data/matchDay.xlsx
@@ -443,7 +443,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1">
-        <v>46130</v>
+        <v>46138</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -451,7 +451,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1">
-        <v>46131</v>
+        <v>46138</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -459,7 +459,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1">
-        <v>46128</v>
+        <v>46137</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -467,7 +467,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1">
-        <v>46128</v>
+        <v>46137</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -475,7 +475,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1">
-        <v>46130</v>
+        <v>46137</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -483,7 +483,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1">
-        <v>46131</v>
+        <v>46137</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1">
-        <v>46129</v>
+        <v>46138</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1">
-        <v>46129</v>
+        <v>46137</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
@@ -507,7 +507,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1">
-        <v>46130</v>
+        <v>46137</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>10</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1">
-        <v>46130</v>
+        <v>46137</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>11</v>
@@ -523,7 +523,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1">
-        <v>46131</v>
+        <v>46136</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -531,7 +531,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1">
-        <v>46131</v>
+        <v>46138</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1">
-        <v>46130</v>
+        <v>46137</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>14</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1">
-        <v>46131</v>
+        <v>46136</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -555,7 +555,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1">
-        <v>46130</v>
+        <v>46138</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -563,7 +563,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1">
-        <v>46129</v>
+        <v>46135</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>17</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1">
-        <v>46131</v>
+        <v>46138</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>18</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1">
-        <v>46129</v>
+        <v>46135</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>19</v>

--- a/Data/matchDay.xlsx
+++ b/Data/matchDay.xlsx
@@ -443,7 +443,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1">
-        <v>46138</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -451,7 +451,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1">
-        <v>46138</v>
+        <v>46144</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -459,7 +459,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1">
-        <v>46137</v>
+        <v>46144</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -467,7 +467,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1">
-        <v>46137</v>
+        <v>46142</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -475,7 +475,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1">
-        <v>46137</v>
+        <v>46144</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -483,7 +483,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1">
-        <v>46137</v>
+        <v>46143</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1">
-        <v>46138</v>
+        <v>46145</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1">
-        <v>46137</v>
+        <v>46144</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
@@ -507,7 +507,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1">
-        <v>46137</v>
+        <v>46145</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>10</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1">
-        <v>46137</v>
+        <v>46142</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>11</v>
@@ -523,7 +523,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1">
-        <v>46136</v>
+        <v>46145</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -531,7 +531,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1">
-        <v>46138</v>
+        <v>46144</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1">
-        <v>46137</v>
+        <v>46143</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>14</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1">
-        <v>46136</v>
+        <v>46144</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -555,7 +555,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1">
-        <v>46138</v>
+        <v>46144</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -563,7 +563,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1">
-        <v>46135</v>
+        <v>46145</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>17</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1">
-        <v>46138</v>
+        <v>46144</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>18</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1">
-        <v>46135</v>
+        <v>46143</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>19</v>

--- a/Data/matchDay.xlsx
+++ b/Data/matchDay.xlsx
@@ -443,7 +443,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1">
-        <v>46143</v>
+        <v>46152</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -451,7 +451,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1">
-        <v>46144</v>
+        <v>46150</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -459,7 +459,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1">
-        <v>46144</v>
+        <v>46150</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -467,7 +467,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1">
-        <v>46142</v>
+        <v>46151</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -475,7 +475,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1">
-        <v>46144</v>
+        <v>46151</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -483,7 +483,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1">
-        <v>46143</v>
+        <v>46149</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1">
-        <v>46145</v>
+        <v>46151</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1">
-        <v>46144</v>
+        <v>46151</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
@@ -507,7 +507,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1">
-        <v>46145</v>
+        <v>46151</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>10</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1">
-        <v>46142</v>
+        <v>46149</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>11</v>
@@ -523,7 +523,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1">
-        <v>46145</v>
+        <v>46152</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -531,7 +531,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1">
-        <v>46144</v>
+        <v>46151</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1">
-        <v>46143</v>
+        <v>46150</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>14</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1">
-        <v>46144</v>
+        <v>46152</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -555,7 +555,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1">
-        <v>46144</v>
+        <v>46151</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -563,7 +563,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1">
-        <v>46145</v>
+        <v>46151</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>17</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1">
-        <v>46144</v>
+        <v>46152</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>18</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1">
-        <v>46143</v>
+        <v>46150</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>19</v>

--- a/Data/matchDay.xlsx
+++ b/Data/matchDay.xlsx
@@ -443,7 +443,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1">
-        <v>46152</v>
+        <v>46158</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -451,7 +451,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1">
-        <v>46150</v>
+        <v>46156</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -459,7 +459,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1">
-        <v>46150</v>
+        <v>46158</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -467,7 +467,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1">
-        <v>46151</v>
+        <v>46157</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -475,7 +475,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1">
-        <v>46151</v>
+        <v>46159</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -483,7 +483,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1">
-        <v>46149</v>
+        <v>46159</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1">
-        <v>46151</v>
+        <v>46159</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1">
-        <v>46151</v>
+        <v>46156</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
@@ -507,7 +507,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1">
-        <v>46151</v>
+        <v>46157</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>10</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1">
-        <v>46149</v>
+        <v>46158</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>11</v>
@@ -523,7 +523,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1">
-        <v>46152</v>
+        <v>46158</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -531,7 +531,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1">
-        <v>46151</v>
+        <v>46158</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>14</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -555,7 +555,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1">
-        <v>46151</v>
+        <v>46159</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -563,7 +563,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1">
-        <v>46151</v>
+        <v>46157</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>17</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>18</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1">
-        <v>46150</v>
+        <v>46158</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>19</v>

--- a/Data/matchDay.xlsx
+++ b/Data/matchDay.xlsx
@@ -443,7 +443,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1">
-        <v>46158</v>
+        <v>46163</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -451,7 +451,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1">
-        <v>46156</v>
+        <v>46166</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -459,7 +459,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1">
-        <v>46158</v>
+        <v>46165</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -467,7 +467,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1">
-        <v>46157</v>
+        <v>46165</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -475,7 +475,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1">
-        <v>46159</v>
+        <v>46164</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -483,7 +483,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1">
-        <v>46159</v>
+        <v>46164</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1">
-        <v>46159</v>
+        <v>46166</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1">
-        <v>46156</v>
+        <v>46165</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
@@ -507,7 +507,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1">
-        <v>46157</v>
+        <v>46165</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>10</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1">
-        <v>46158</v>
+        <v>46163</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>11</v>
@@ -523,7 +523,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1">
-        <v>46158</v>
+        <v>46166</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -531,7 +531,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1">
-        <v>46158</v>
+        <v>46165</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1">
-        <v>46157</v>
+        <v>46165</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>14</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1">
-        <v>46159</v>
+        <v>46164</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -555,7 +555,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1">
-        <v>46159</v>
+        <v>46164</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -563,7 +563,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1">
-        <v>46157</v>
+        <v>46165</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>17</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1">
-        <v>46159</v>
+        <v>46165</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>18</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1">
-        <v>46158</v>
+        <v>46166</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>19</v>

--- a/Data/matchDay.xlsx
+++ b/Data/matchDay.xlsx
@@ -451,7 +451,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1">
-        <v>46166</v>
+        <v>46172</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -459,7 +459,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1">
-        <v>46165</v>
+        <v>46171</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -467,7 +467,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1">
-        <v>46165</v>
+        <v>46172</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -475,7 +475,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1">
-        <v>46164</v>
+        <v>46173</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -483,7 +483,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1">
-        <v>46164</v>
+        <v>46172</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1">
-        <v>46166</v>
+        <v>46173</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1">
-        <v>46165</v>
+        <v>46171</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1">
-        <v>46163</v>
+        <v>46170</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>11</v>
@@ -523,7 +523,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1">
-        <v>46166</v>
+        <v>46173</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1">
-        <v>46164</v>
+        <v>46172</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -555,7 +555,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1">
-        <v>46164</v>
+        <v>46170</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -563,7 +563,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1">
-        <v>46165</v>
+        <v>46172</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>17</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1">
-        <v>46165</v>
+        <v>46173</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>18</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1">
-        <v>46166</v>
+        <v>46172</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>19</v>

--- a/Data/matchDay.xlsx
+++ b/Data/matchDay.xlsx
@@ -443,7 +443,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1">
-        <v>46163</v>
+        <v>46177</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -451,7 +451,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1">
-        <v>46172</v>
+        <v>46179</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -459,7 +459,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1">
-        <v>46171</v>
+        <v>46180</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -467,7 +467,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1">
-        <v>46172</v>
+        <v>46181</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -475,7 +475,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1">
-        <v>46173</v>
+        <v>46180</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -483,7 +483,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1">
-        <v>46172</v>
+        <v>46179</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1">
-        <v>46171</v>
+        <v>46177</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
@@ -507,7 +507,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1">
-        <v>46165</v>
+        <v>46179</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>10</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1">
-        <v>46170</v>
+        <v>46178</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>11</v>
@@ -523,7 +523,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1">
-        <v>46173</v>
+        <v>46181</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -531,7 +531,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1">
-        <v>46165</v>
+        <v>46179</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1">
-        <v>46165</v>
+        <v>46179</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>14</v>
@@ -555,7 +555,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1">
-        <v>46170</v>
+        <v>46180</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -563,7 +563,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1">
-        <v>46172</v>
+        <v>46180</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>17</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1">
-        <v>46173</v>
+        <v>46179</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>18</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1">
-        <v>46172</v>
+        <v>46178</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>19</v>

--- a/Data/matchDay.xlsx
+++ b/Data/matchDay.xlsx
@@ -443,7 +443,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1">
-        <v>46177</v>
+        <v>46184</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -451,7 +451,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1">
-        <v>46179</v>
+        <v>46187</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -475,7 +475,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1">
-        <v>46180</v>
+        <v>46186</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1">
-        <v>46173</v>
+        <v>46187</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1">
-        <v>46177</v>
+        <v>46185</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
@@ -507,7 +507,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1">
-        <v>46179</v>
+        <v>46185</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>10</v>
@@ -523,7 +523,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1">
-        <v>46181</v>
+        <v>46186</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -531,7 +531,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1">
-        <v>46179</v>
+        <v>46186</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1">
-        <v>46179</v>
+        <v>46186</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>14</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1">
-        <v>46172</v>
+        <v>46187</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -555,7 +555,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1">
-        <v>46180</v>
+        <v>46187</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -563,7 +563,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1">
-        <v>46180</v>
+        <v>46186</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>17</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1">
-        <v>46179</v>
+        <v>46186</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>18</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1">
-        <v>46178</v>
+        <v>46184</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>19</v>

--- a/Data/matchDay.xlsx
+++ b/Data/matchDay.xlsx
@@ -443,7 +443,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1">
-        <v>46184</v>
+        <v>46193</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -459,7 +459,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1">
-        <v>46180</v>
+        <v>46193</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -467,7 +467,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1">
-        <v>46181</v>
+        <v>46193</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -483,7 +483,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1">
-        <v>46179</v>
+        <v>46191</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1">
-        <v>46187</v>
+        <v>46193</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1">
-        <v>46185</v>
+        <v>46191</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
@@ -507,7 +507,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1">
-        <v>46185</v>
+        <v>46192</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>10</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1">
-        <v>46178</v>
+        <v>46192</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>11</v>
@@ -523,7 +523,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -531,7 +531,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1">
-        <v>46186</v>
+        <v>46194</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1">
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>14</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1">
-        <v>46187</v>
+        <v>46194</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -555,7 +555,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1">
-        <v>46187</v>
+        <v>46194</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1">
-        <v>46184</v>
+        <v>46194</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>19</v>

--- a/Data/matchDay.xlsx
+++ b/Data/matchDay.xlsx
@@ -443,7 +443,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -451,7 +451,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1">
-        <v>46187</v>
+        <v>46198</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -459,7 +459,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -467,7 +467,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -475,7 +475,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1">
-        <v>46186</v>
+        <v>46201</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -483,7 +483,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1">
-        <v>46191</v>
+        <v>46201</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1">
-        <v>46193</v>
+        <v>46199</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
@@ -507,7 +507,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1">
-        <v>46192</v>
+        <v>46201</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>10</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1">
-        <v>46192</v>
+        <v>46199</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>11</v>
@@ -531,7 +531,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1">
-        <v>46194</v>
+        <v>46201</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1">
-        <v>46193</v>
+        <v>46200</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>14</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1">
-        <v>46194</v>
+        <v>46200</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -563,7 +563,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1">
-        <v>46186</v>
+        <v>46198</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>17</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1">
-        <v>46186</v>
+        <v>46200</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>18</v>

--- a/Data/matchDay.xlsx
+++ b/Data/matchDay.xlsx
@@ -443,7 +443,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1">
-        <v>46200</v>
+        <v>46206</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -451,7 +451,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1">
-        <v>46198</v>
+        <v>46205</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -459,7 +459,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1">
-        <v>46200</v>
+        <v>46207</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -467,7 +467,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1">
-        <v>46200</v>
+        <v>46207</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -475,7 +475,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1">
-        <v>46201</v>
+        <v>46208</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -483,7 +483,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1">
-        <v>46201</v>
+        <v>46207</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1">
-        <v>46199</v>
+        <v>46207</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1">
-        <v>46191</v>
+        <v>46205</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
@@ -507,7 +507,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1">
-        <v>46201</v>
+        <v>46207</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>10</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1">
-        <v>46199</v>
+        <v>46207</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>11</v>
@@ -523,7 +523,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1">
-        <v>46193</v>
+        <v>46207</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -531,7 +531,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1">
-        <v>46201</v>
+        <v>46208</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1">
-        <v>46200</v>
+        <v>46208</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>14</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1">
-        <v>46200</v>
+        <v>46207</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -555,7 +555,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1">
-        <v>46194</v>
+        <v>46208</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -563,7 +563,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1">
-        <v>46198</v>
+        <v>46206</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>17</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1">
-        <v>46200</v>
+        <v>46206</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>18</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1">
-        <v>46194</v>
+        <v>46206</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>19</v>

--- a/Data/matchDay.xlsx
+++ b/Data/matchDay.xlsx
@@ -443,7 +443,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1">
-        <v>46206</v>
+        <v>46214</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -451,7 +451,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1">
-        <v>46205</v>
+        <v>46215</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -459,7 +459,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -467,7 +467,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1">
-        <v>46207</v>
+        <v>46213</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -475,7 +475,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1">
-        <v>46208</v>
+        <v>46215</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -483,7 +483,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1">
-        <v>46207</v>
+        <v>46212</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1">
-        <v>46205</v>
+        <v>46214</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
@@ -507,7 +507,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>10</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1">
-        <v>46207</v>
+        <v>46214</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>11</v>
@@ -523,7 +523,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1">
-        <v>46207</v>
+        <v>46215</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -531,7 +531,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1">
-        <v>46208</v>
+        <v>46213</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>14</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1">
-        <v>46207</v>
+        <v>46215</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -555,7 +555,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1">
-        <v>46208</v>
+        <v>46214</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -563,7 +563,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1">
-        <v>46206</v>
+        <v>46212</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>17</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1">
-        <v>46206</v>
+        <v>46215</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>18</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1">
-        <v>46206</v>
+        <v>46215</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>19</v>

--- a/Data/matchDay.xlsx
+++ b/Data/matchDay.xlsx
@@ -443,7 +443,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1">
-        <v>46214</v>
+        <v>46220</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -451,7 +451,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -459,7 +459,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>4</v>
@@ -467,7 +467,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1">
-        <v>46213</v>
+        <v>46221</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
@@ -475,7 +475,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="1">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>6</v>
@@ -483,7 +483,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="1">
-        <v>46212</v>
+        <v>46221</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="1">
-        <v>46214</v>
+        <v>46222</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1">
-        <v>46214</v>
+        <v>46219</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>9</v>
@@ -507,7 +507,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="1">
-        <v>46214</v>
+        <v>46222</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>10</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="1">
-        <v>46214</v>
+        <v>46222</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>11</v>
@@ -523,7 +523,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -531,7 +531,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1">
-        <v>46213</v>
+        <v>46221</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1">
-        <v>46214</v>
+        <v>46221</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>14</v>
@@ -547,7 +547,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -555,7 +555,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1">
-        <v>46214</v>
+        <v>46219</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -563,7 +563,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1">
-        <v>46212</v>
+        <v>46220</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>17</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1">
-        <v>46215</v>
+        <v>46221</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>18</v>
@@ -579,7 +579,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1">
-        <v>46215</v>
+        <v>46222</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>19</v>
